--- a/data/raw/inventory/Week 28/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>afn_fulfillable_quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>afn_inbound_working_quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>afn_inbound_shipped_quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>afn_inbound_receiving_quantity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>afn_reserved_quantity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>afn_total_quantity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>afn_unsellable_quantity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>afn_researching_quantity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seller Account</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
@@ -597,7 +585,7 @@
         <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>15</v>
@@ -609,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>26</v>
@@ -783,7 +771,7 @@
         <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -795,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>39</v>
@@ -2144,13 +2132,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2162,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2398,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
         <v>4</v>
@@ -2407,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>10</v>
@@ -2640,7 +2628,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F36" t="n">
         <v>60</v>
@@ -2655,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3511,7 +3499,7 @@
         <v>24</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3523,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>25</v>
@@ -3942,13 +3930,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -3960,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4252,7 +4240,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F62" t="n">
         <v>10</v>
@@ -4267,10 +4255,10 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L62" t="n">
         <v>2</v>
@@ -4996,7 +4984,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F74" t="n">
         <v>23</v>
@@ -5011,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -5309,7 +5297,7 @@
         <v>31</v>
       </c>
       <c r="F79" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -5321,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K79" t="n">
         <v>31</v>
@@ -7603,7 +7591,7 @@
         <v>14</v>
       </c>
       <c r="F116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -7615,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
         <v>14</v>
@@ -8719,7 +8707,7 @@
         <v>17</v>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
         <v>15</v>
@@ -8731,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134" t="n">
         <v>19</v>
@@ -9026,7 +9014,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F139" t="n">
         <v>19</v>
@@ -9041,10 +9029,10 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K139" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -11134,7 +11122,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F173" t="n">
         <v>53</v>
@@ -11149,10 +11137,10 @@
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K173" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -11320,7 +11308,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F176" t="n">
         <v>6</v>
@@ -11335,10 +11323,10 @@
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>

--- a/data/raw/inventory/Week 28/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 28/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F2" t="n">
         <v>143</v>
@@ -535,10 +535,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -582,25 +582,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>15</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -647,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>8</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>5</v>
@@ -1515,7 +1515,7 @@
         <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>59</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -1952,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2014,10 +2014,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
         <v>2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>1</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2383,19 +2383,19 @@
         <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>10</v>
@@ -2448,10 +2448,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
         <v>1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F34" t="n">
         <v>14</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L34" t="n">
         <v>1</v>
@@ -2569,7 +2569,7 @@
         <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>25</v>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F36" t="n">
         <v>60</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2758,10 +2758,10 @@
         <v>25</v>
       </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>40</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2944,10 +2944,10 @@
         <v>2</v>
       </c>
       <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>2</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3124,13 +3124,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F48" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
         <v>14</v>
       </c>
       <c r="F60" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G60" t="n">
         <v>2</v>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>14</v>
@@ -4243,7 +4243,7 @@
         <v>40</v>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G62" t="n">
         <v>30</v>
@@ -4255,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>42</v>
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F66" t="n">
         <v>21</v>
@@ -4503,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         <v>5</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -4689,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>9</v>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -4875,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K72" t="n">
         <v>9</v>
@@ -4987,7 +4987,7 @@
         <v>24</v>
       </c>
       <c r="F74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
         <v>24</v>
@@ -5176,10 +5176,10 @@
         <v>4</v>
       </c>
       <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
         <v>5</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F79" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -5312,7 +5312,7 @@
         <v>5</v>
       </c>
       <c r="K79" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F84" t="n">
         <v>86</v>
@@ -5619,10 +5619,10 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L84" t="n">
         <v>1</v>
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F87" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
         <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L87" t="n">
         <v>1</v>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F88" t="n">
         <v>39</v>
@@ -5867,10 +5867,10 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>44</v>
       </c>
       <c r="F90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -5991,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K90" t="n">
         <v>44</v>
@@ -6168,10 +6168,10 @@
         <v>4</v>
       </c>
       <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
         <v>3</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -6413,7 +6413,7 @@
         <v>7</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K97" t="n">
         <v>7</v>
@@ -6785,7 +6785,7 @@
         <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
         <v>2</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F106" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -7033,19 +7033,19 @@
         <v>38</v>
       </c>
       <c r="F107" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
         <v>20</v>
       </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107" t="n">
         <v>38</v>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F114" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -7479,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -7780,10 +7780,10 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
         <v>6</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -7836,13 +7836,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F120" t="n">
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -7854,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L120" t="n">
         <v>1</v>
@@ -7898,16 +7898,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
         <v>10</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -7916,7 +7916,7 @@
         <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L121" t="n">
         <v>1</v>
@@ -8214,10 +8214,10 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
         <v>20</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -8270,7 +8270,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F127" t="n">
         <v>93</v>
@@ -8285,10 +8285,10 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K127" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F128" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G128" t="n">
         <v>5</v>
@@ -8350,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -8524,10 +8524,10 @@
         <v>7</v>
       </c>
       <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
         <v>8</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -8586,10 +8586,10 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
         <v>4</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F134" t="n">
         <v>1</v>
@@ -8719,10 +8719,10 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L134" t="n">
         <v>2</v>
@@ -8893,7 +8893,7 @@
         <v>35</v>
       </c>
       <c r="F137" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" t="n">
         <v>35</v>
@@ -9017,7 +9017,7 @@
         <v>20</v>
       </c>
       <c r="F139" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
         <v>20</v>
@@ -9516,10 +9516,10 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
         <v>3</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -10322,10 +10322,10 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
         <v>10</v>
-      </c>
-      <c r="H160" t="n">
-        <v>0</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
@@ -10508,10 +10508,10 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
         <v>4</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -10570,10 +10570,10 @@
         <v>14</v>
       </c>
       <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
         <v>8</v>
-      </c>
-      <c r="H164" t="n">
-        <v>0</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -10632,10 +10632,10 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I165" t="n">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
@@ -10765,10 +10765,10 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
         <v>1</v>
-      </c>
-      <c r="K167" t="n">
-        <v>2</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F168" t="n">
         <v>1</v>
@@ -10827,10 +10827,10 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
+        <v>1</v>
+      </c>
+      <c r="K168" t="n">
         <v>2</v>
-      </c>
-      <c r="K168" t="n">
-        <v>3</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F171" t="n">
         <v>22</v>
@@ -11013,10 +11013,10 @@
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F173" t="n">
         <v>53</v>
@@ -11137,10 +11137,10 @@
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K173" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -11184,10 +11184,10 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -11202,7 +11202,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L174" t="n">
         <v>1</v>
@@ -11388,10 +11388,10 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -12303,7 +12303,7 @@
         <v>34</v>
       </c>
       <c r="F192" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -12315,7 +12315,7 @@
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K192" t="n">
         <v>34</v>
